--- a/src/content/setListNevro.xlsx
+++ b/src/content/setListNevro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabien/depotsGitHub/nevrosyne-site/src/content/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD3509B-E788-8740-BB8C-D71A5EAA46FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255ADB5F-9E4B-F546-9C7E-9F6059B92DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23360" yWindow="11220" windowWidth="27640" windowHeight="16680" xr2:uid="{2BD5CEB2-7970-AF41-AD76-FF08FE45782D}"/>
+    <workbookView xWindow="7620" yWindow="680" windowWidth="32500" windowHeight="28660" xr2:uid="{2BD5CEB2-7970-AF41-AD76-FF08FE45782D}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="115">
   <si>
     <t>num</t>
   </si>
@@ -77,12 +77,6 @@
     <t>Elvis Presley</t>
   </si>
   <si>
-    <t>Another one bites the dust / Machistador</t>
-  </si>
-  <si>
-    <t>Queen + M Nevro ver.</t>
-  </si>
-  <si>
     <t>Are U gonna be my girl</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>Ca c’est vraiment toi</t>
   </si>
   <si>
-    <t>Téléphone</t>
-  </si>
-  <si>
     <t>Colors</t>
   </si>
   <si>
@@ -149,9 +140,6 @@
     <t>Offspring</t>
   </si>
   <si>
-    <t>Complexe du corn flakes</t>
-  </si>
-  <si>
     <t>Mathieu Chédid</t>
   </si>
   <si>
@@ -161,12 +149,6 @@
     <t>Patti Smith</t>
   </si>
   <si>
-    <t>Eye of the tiger</t>
-  </si>
-  <si>
-    <t>Survivor</t>
-  </si>
-  <si>
     <t>Girls just want to have fun</t>
   </si>
   <si>
@@ -188,12 +170,6 @@
     <t>Eurythmics</t>
   </si>
   <si>
-    <t>I love rock n roll</t>
-  </si>
-  <si>
-    <t>Joan Jett</t>
-  </si>
-  <si>
     <t>I'm Picky</t>
   </si>
   <si>
@@ -245,12 +221,6 @@
     <t>Indochine</t>
   </si>
   <si>
-    <t>Left outside alone</t>
-  </si>
-  <si>
-    <t>Anastacia</t>
-  </si>
-  <si>
     <t>Make it wit chu</t>
   </si>
   <si>
@@ -278,12 +248,6 @@
     <t>Muse</t>
   </si>
   <si>
-    <t>Price tag</t>
-  </si>
-  <si>
-    <t>Jessie J</t>
-  </si>
-  <si>
     <t>Psycho</t>
   </si>
   <si>
@@ -338,12 +302,6 @@
     <t>Jean-Louis Aubert</t>
   </si>
   <si>
-    <t>This world</t>
-  </si>
-  <si>
-    <t>Selah Sue</t>
-  </si>
-  <si>
     <t>Time is running out</t>
   </si>
   <si>
@@ -381,6 +339,51 @@
   </si>
   <si>
     <t>Tears for fear - Nevro ver</t>
+  </si>
+  <si>
+    <t>Téléphone  - Nevro ver</t>
+  </si>
+  <si>
+    <t>Despair Hangover and Ecstasy</t>
+  </si>
+  <si>
+    <t>The Do - Nevro ver</t>
+  </si>
+  <si>
+    <t>Get Free</t>
+  </si>
+  <si>
+    <t>The vines</t>
+  </si>
+  <si>
+    <t>Girls and Boys</t>
+  </si>
+  <si>
+    <t>Blur - Nevro ver</t>
+  </si>
+  <si>
+    <t>La isla Bonita</t>
+  </si>
+  <si>
+    <t>Madonna - Nevro ver</t>
+  </si>
+  <si>
+    <t>Smalltown Forest</t>
+  </si>
+  <si>
+    <t>The Cure / Jimmy summerville - Nevro ver</t>
+  </si>
+  <si>
+    <t>Whole lotta Rosie</t>
+  </si>
+  <si>
+    <t>ACDC</t>
+  </si>
+  <si>
+    <t>Wonderfull life</t>
+  </si>
+  <si>
+    <t>Black - Nevro ver</t>
   </si>
 </sst>
 </file>
@@ -864,7 +867,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="4">
-        <v>2.488425925925926E-3</v>
+        <v>2.4768518518518516E-3</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -878,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="4">
-        <v>2.4768518518518516E-3</v>
+        <v>2.4537037037037036E-3</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -892,7 +895,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="4">
-        <v>2.4537037037037036E-3</v>
+        <v>2.7893518518518519E-3</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -906,7 +909,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="4">
-        <v>2.7893518518518519E-3</v>
+        <v>2.2453703703703702E-3</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -920,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="4">
-        <v>2.2453703703703702E-3</v>
+        <v>2.4537037037037036E-3</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -934,7 +937,7 @@
         <v>23</v>
       </c>
       <c r="D11" s="4">
-        <v>2.4537037037037036E-3</v>
+        <v>3.425925925925926E-3</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -948,7 +951,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="4">
-        <v>3.425925925925926E-3</v>
+        <v>1.8634259259259261E-3</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -962,7 +965,7 @@
         <v>27</v>
       </c>
       <c r="D13" s="4">
-        <v>1.8634259259259261E-3</v>
+        <v>2.1296296296296298E-3</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -973,10 +976,10 @@
         <v>28</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="D14" s="4">
-        <v>2.1296296296296298E-3</v>
+        <v>3.1018518518518522E-3</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -984,13 +987,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="D15" s="4">
-        <v>3.1018518518518522E-3</v>
+        <v>2.8587962962962963E-3</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -998,13 +1001,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="D16" s="4">
-        <v>2.8587962962962963E-3</v>
+        <v>2.2916666666666667E-3</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1018,7 +1021,7 @@
         <v>35</v>
       </c>
       <c r="D17" s="4">
-        <v>2.2916666666666667E-3</v>
+        <v>2.9629629629629628E-3</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1026,13 +1029,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>37</v>
+        <v>102</v>
       </c>
       <c r="D18" s="4">
-        <v>3.3796296296296296E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1040,13 +1043,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="D19" s="4">
-        <v>2.9629629629629628E-3</v>
+        <v>1.5277777777777779E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1054,13 +1057,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="D20" s="4">
-        <v>2.8472222222222219E-3</v>
+        <v>3.2407407407407406E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1068,10 +1071,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D21" s="4">
         <v>2.7199074074074074E-3</v>
@@ -1082,7 +1085,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>5</v>
@@ -1096,10 +1099,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D23" s="4">
         <v>2.4189814814814816E-3</v>
@@ -1110,10 +1113,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D24" s="4">
         <v>1.5046296296296294E-3</v>
@@ -1124,13 +1127,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D25" s="4">
-        <v>2.0254629629629629E-3</v>
+        <v>2.7546296296296294E-3</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1138,13 +1141,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D26" s="4">
-        <v>2.7546296296296294E-3</v>
+        <v>1.7824074074074072E-3</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1152,13 +1155,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D27" s="4">
-        <v>1.7824074074074072E-3</v>
+        <v>2.6504629629629625E-3</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1166,13 +1169,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D28" s="4">
-        <v>2.6504629629629625E-3</v>
+        <v>2.1296296296296298E-3</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1180,13 +1183,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D29" s="4">
-        <v>2.1296296296296298E-3</v>
+        <v>2.7314814814814819E-3</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1194,13 +1197,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D30" s="4">
-        <v>2.7314814814814819E-3</v>
+        <v>2.3842592592592591E-3</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1208,13 +1211,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D31" s="4">
-        <v>2.3842592592592591E-3</v>
+        <v>3.6342592592592594E-3</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1222,13 +1225,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D32" s="4">
-        <v>3.6342592592592594E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1236,13 +1239,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D33" s="4">
-        <v>3.472222222222222E-3</v>
+        <v>2.685185185185185E-3</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1250,13 +1253,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="D34" s="4">
-        <v>2.685185185185185E-3</v>
+        <v>2.8124999999999999E-3</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1264,13 +1267,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D35" s="4">
-        <v>2.9745370370370373E-3</v>
+        <v>3.3564814814814811E-3</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1278,13 +1281,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D36" s="4">
-        <v>3.3564814814814811E-3</v>
+        <v>4.1666666666666666E-3</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1292,10 +1295,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="D37" s="4">
         <v>4.1666666666666666E-3</v>
@@ -1306,13 +1309,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="D38" s="4">
-        <v>4.1666666666666666E-3</v>
+        <v>2.1643518518518518E-3</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1320,13 +1323,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D39" s="4">
-        <v>2.1643518518518518E-3</v>
+        <v>2.5462962962962961E-3</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1334,13 +1337,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D40" s="4">
-        <v>2.5462962962962961E-3</v>
+        <v>3.6689814814814814E-3</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1348,13 +1351,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D41" s="4">
-        <v>2.5810185185185185E-3</v>
+        <v>4.8611111111111112E-3</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1362,13 +1365,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D42" s="4">
-        <v>3.6689814814814814E-3</v>
+        <v>4.5486111111111109E-3</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1376,13 +1379,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D43" s="4">
-        <v>4.8611111111111112E-3</v>
+        <v>2.9166666666666668E-3</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1390,13 +1393,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D44" s="4">
-        <v>4.5486111111111109E-3</v>
+        <v>3.3449074074074076E-3</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1404,13 +1407,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="D45" s="4">
-        <v>2.9166666666666668E-3</v>
+        <v>3.483796296296296E-3</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1418,13 +1421,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="D46" s="4">
-        <v>3.483796296296296E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1432,13 +1435,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D47" s="4">
-        <v>2.0833333333333333E-3</v>
+        <v>2.9398148148148148E-3</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1446,13 +1449,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D48" s="4">
-        <v>2.9398148148148148E-3</v>
+        <v>3.3680555555555551E-3</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1460,13 +1463,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D49" s="4">
-        <v>3.3680555555555551E-3</v>
+        <v>1.7824074074074075E-3</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1474,13 +1477,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D50" s="4">
-        <v>1.7824074074074075E-3</v>
+        <v>2.7662037037037034E-3</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1488,13 +1491,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D51" s="4">
-        <v>2.7662037037037034E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1502,13 +1505,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="D52" s="4">
-        <v>3.472222222222222E-3</v>
+        <v>2.7430555555555559E-3</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1516,13 +1519,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D53" s="4">
-        <v>3.3101851851851851E-3</v>
+        <v>2.5347222222222221E-3</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1530,13 +1533,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D54" s="4">
-        <v>2.7430555555555559E-3</v>
+        <v>2.3726851851851851E-3</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1544,13 +1547,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D55" s="4">
-        <v>2.5347222222222221E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1558,13 +1561,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D56" s="4">
-        <v>2.3726851851851851E-3</v>
+        <v>2.6967592592592594E-3</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1572,13 +1575,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D57" s="4">
-        <v>3.472222222222222E-3</v>
+        <v>3.1365740740740742E-3</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1586,13 +1589,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D58" s="4">
-        <v>2.6967592592592594E-3</v>
+        <v>3.3333333333333335E-3</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="19" x14ac:dyDescent="0.25">
@@ -1600,10 +1603,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D59" s="4">
         <v>3.5532407407407405E-3</v>
